--- a/БД/funcs/LVALH.xlsx
+++ b/БД/funcs/LVALH.xlsx
@@ -1055,7 +1055,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1095,6 +1095,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1160,7 +1166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1308,12 +1314,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1338,6 +1338,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1742,15 +1751,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="54"/>
-      <c r="BB1" s="54"/>
-      <c r="BC1" s="54"/>
-      <c r="BD1" s="54"/>
-      <c r="BE1" s="54"/>
-      <c r="BF1" s="54"/>
+      <c r="AZ1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -1894,13 +1903,13 @@
       <c r="AU2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="AV2" s="60" t="s">
+      <c r="AV2" s="58" t="s">
         <v>312</v>
       </c>
-      <c r="AW2" s="60" t="s">
+      <c r="AW2" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="AX2" s="60" t="s">
+      <c r="AX2" s="58" t="s">
         <v>314</v>
       </c>
       <c r="AY2" s="19"/>
@@ -18251,7 +18260,7 @@
     </row>
     <row r="3" spans="1:16379" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>315</v>
       </c>
       <c r="C3" s="24"/>
@@ -18341,22 +18350,20 @@
       <c r="AS3" s="31">
         <v>0</v>
       </c>
-      <c r="AT3" s="31">
-        <v>0</v>
+      <c r="AT3" s="64">
+        <v>1</v>
       </c>
       <c r="AU3" s="31">
         <v>0</v>
       </c>
-      <c r="AV3" s="31">
-        <f t="shared" ref="AV3" si="2">BIN2DEC(CONCATENATE(0,0,0,0,AR3,AS3,AT3,AU3))</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="31">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="31">
-        <f t="shared" ref="AX3:AX40" si="3">BIN2DEC(CONCATENATE(0,0,0,0,AT3,AU3,AV3,AW3))</f>
-        <v>0</v>
+      <c r="AV3" s="64">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="64">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="64">
+        <v>1</v>
       </c>
       <c r="AY3" s="31"/>
       <c r="AZ3" s="28"/>
@@ -18367,7 +18374,7 @@
       <c r="BE3" s="35"/>
       <c r="BF3" s="31"/>
       <c r="BG3" s="36" t="str">
-        <f t="shared" ref="BG3" si="4">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
+        <f t="shared" ref="BG3" si="2">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
         <v>description: "Вывод терминала", note: "Вывод терминала", group: "control", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH3" s="37"/>
@@ -18390,7 +18397,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="25">
-        <f t="shared" ref="I4:I6" si="5">LEN(F4)</f>
+        <f t="shared" ref="I4:I6" si="3">LEN(F4)</f>
         <v>19</v>
       </c>
       <c r="J4" s="25" t="str">
@@ -18471,14 +18478,14 @@
         <v>0</v>
       </c>
       <c r="AV4" s="31">
-        <f t="shared" ref="AV4:AV6" si="6">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
+        <f t="shared" ref="AV4:AV6" si="4">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
         <v>0</v>
       </c>
       <c r="AW4" s="31">
         <v>0</v>
       </c>
       <c r="AX4" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AX3:AX40" si="5">BIN2DEC(CONCATENATE(0,0,0,0,AT4,AU4,AV4,AW4))</f>
         <v>0</v>
       </c>
       <c r="AY4" s="31"/>
@@ -18490,7 +18497,7 @@
       <c r="BE4" s="35"/>
       <c r="BF4" s="31"/>
       <c r="BG4" s="36" t="str">
-        <f t="shared" ref="BG4:BG6" si="7">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
+        <f t="shared" ref="BG4:BG6" si="6">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
         <v>description: "Ср.сигн. ДЗ-фф 1ст.", note: "Срабатывание на сигнал 1 ступени ДЗ-фф", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH4" s="37"/>
@@ -18513,7 +18520,7 @@
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="J5" s="25" t="str">
@@ -18594,14 +18601,14 @@
         <v>0</v>
       </c>
       <c r="AV5" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW5" s="31">
         <v>0</v>
       </c>
       <c r="AX5" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY5" s="31"/>
@@ -18613,7 +18620,7 @@
       <c r="BE5" s="35"/>
       <c r="BF5" s="31"/>
       <c r="BG5" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Ср.сигн. ДЗ-фф 2ст.", note: "Срабатывание на сигнал 2 ступени ДЗ-фф", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH5" s="37"/>
@@ -18636,7 +18643,7 @@
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="J6" s="25" t="str">
@@ -18717,14 +18724,14 @@
         <v>0</v>
       </c>
       <c r="AV6" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW6" s="31">
         <v>0</v>
       </c>
       <c r="AX6" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY6" s="31"/>
@@ -18736,7 +18743,7 @@
       <c r="BE6" s="35"/>
       <c r="BF6" s="31"/>
       <c r="BG6" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Ср.сигн. ДЗ-фф 3ст.", note: "Срабатывание на сигнал 3 ступени ДЗ-фф", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH6" s="37"/>
@@ -18759,7 +18766,7 @@
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <f t="shared" ref="I7:I8" si="8">LEN(F7)</f>
+        <f t="shared" ref="I7:I8" si="7">LEN(F7)</f>
         <v>19</v>
       </c>
       <c r="J7" s="25" t="str">
@@ -18840,14 +18847,14 @@
         <v>0</v>
       </c>
       <c r="AV7" s="31">
-        <f t="shared" ref="AV7:AV8" si="9">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
+        <f t="shared" ref="AV7:AV8" si="8">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
         <v>0</v>
       </c>
       <c r="AW7" s="31">
         <v>0</v>
       </c>
       <c r="AX7" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY7" s="31"/>
@@ -18859,7 +18866,7 @@
       <c r="BE7" s="35"/>
       <c r="BF7" s="31"/>
       <c r="BG7" s="36" t="str">
-        <f t="shared" ref="BG7:BG8" si="10">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
+        <f t="shared" ref="BG7:BG8" si="9">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
         <v>description: "Ср.сигн. ДЗ-фз 1ст.", note: "Срабатывание на сигнал 1 ступени ДЗ-фз", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH7" s="37"/>
@@ -18882,7 +18889,7 @@
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="J8" s="25" t="str">
@@ -18963,14 +18970,14 @@
         <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AW8" s="31">
         <v>0</v>
       </c>
       <c r="AX8" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY8" s="31"/>
@@ -18982,7 +18989,7 @@
       <c r="BE8" s="35"/>
       <c r="BF8" s="31"/>
       <c r="BG8" s="36" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>description: "Ср.сигн. ДЗ-фз 2ст.", note: "Срабатывание на сигнал 2 ступени ДЗ-фз", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH8" s="37"/>
@@ -19005,11 +19012,11 @@
       </c>
       <c r="H9" s="25"/>
       <c r="I9" s="25">
-        <f t="shared" ref="I9:I32" si="11">LEN(F9)</f>
+        <f t="shared" ref="I9:I32" si="10">LEN(F9)</f>
         <v>19</v>
       </c>
       <c r="J9" s="25" t="str">
-        <f t="shared" ref="J9:J32" si="12">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
+        <f t="shared" ref="J9:J32" si="11">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
         <v>Ср.сигн.ВыхЛогНЗОЗЗ</v>
       </c>
       <c r="K9" s="23" t="s">
@@ -19086,14 +19093,14 @@
         <v>0</v>
       </c>
       <c r="AV9" s="31">
-        <f t="shared" ref="AV9:AV32" si="13">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
+        <f t="shared" ref="AV9:AV32" si="12">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
         <v>0</v>
       </c>
       <c r="AW9" s="31">
         <v>0</v>
       </c>
       <c r="AX9" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY9" s="31"/>
@@ -19105,7 +19112,7 @@
       <c r="BE9" s="35"/>
       <c r="BF9" s="31"/>
       <c r="BG9" s="36" t="str">
-        <f t="shared" ref="BG9:BG32" si="14">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
+        <f t="shared" ref="BG9:BG32" si="13">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
         <v>description: "Ср.сигн.ВыхЛогНЗОЗЗ", note: "Срабатывание на сигнал ВыхЛогНЗОЗЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH9" s="37"/>
@@ -19128,11 +19135,11 @@
       </c>
       <c r="H10" s="25"/>
       <c r="I10" s="25">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J10" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="J10" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ТЗНП 1 ст.</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -19209,14 +19216,14 @@
         <v>0</v>
       </c>
       <c r="AV10" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW10" s="31">
         <v>0</v>
       </c>
       <c r="AX10" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY10" s="31"/>
@@ -19228,7 +19235,7 @@
       <c r="BE10" s="35"/>
       <c r="BF10" s="31"/>
       <c r="BG10" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ТЗНП 1 ст.", note: "Срабатывание на сигнал 1 ступени ТЗНП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH10" s="37"/>
@@ -19251,11 +19258,11 @@
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J11" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="J11" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ТЗНП 2 ст.</v>
       </c>
       <c r="K11" s="23" t="s">
@@ -19332,14 +19339,14 @@
         <v>0</v>
       </c>
       <c r="AV11" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW11" s="31">
         <v>0</v>
       </c>
       <c r="AX11" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY11" s="31"/>
@@ -19351,7 +19358,7 @@
       <c r="BE11" s="35"/>
       <c r="BF11" s="31"/>
       <c r="BG11" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ТЗНП 2 ст.", note: "Срабатывание на сигнал 2 ступени ТЗНП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH11" s="37"/>
@@ -19374,11 +19381,11 @@
       </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="J12" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>11</v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ТО</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -19455,14 +19462,14 @@
         <v>0</v>
       </c>
       <c r="AV12" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW12" s="31">
         <v>0</v>
       </c>
       <c r="AX12" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY12" s="31"/>
@@ -19474,7 +19481,7 @@
       <c r="BE12" s="35"/>
       <c r="BF12" s="31"/>
       <c r="BG12" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ТО", note: "Срабатывание на сигнал ТО", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH12" s="37"/>
@@ -19497,11 +19504,11 @@
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J13" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J13" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. МТЗ 1 ст.</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -19578,14 +19585,14 @@
         <v>0</v>
       </c>
       <c r="AV13" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW13" s="31">
         <v>0</v>
       </c>
       <c r="AX13" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY13" s="31"/>
@@ -19597,7 +19604,7 @@
       <c r="BE13" s="35"/>
       <c r="BF13" s="31"/>
       <c r="BG13" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. МТЗ 1 ст.", note: "Срабатывание на сигнал 1 ступени МТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH13" s="37"/>
@@ -19620,11 +19627,11 @@
       </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J14" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J14" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. МТЗ 2 ст.</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -19701,14 +19708,14 @@
         <v>0</v>
       </c>
       <c r="AV14" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW14" s="31">
         <v>0</v>
       </c>
       <c r="AX14" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY14" s="31"/>
@@ -19720,7 +19727,7 @@
       <c r="BE14" s="35"/>
       <c r="BF14" s="31"/>
       <c r="BG14" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. МТЗ 2 ст.", note: "Срабатывание на сигнал 2 ступени МТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH14" s="37"/>
@@ -19743,11 +19750,11 @@
       </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J15" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J15" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. МТЗ 3 ст.</v>
       </c>
       <c r="K15" s="23" t="s">
@@ -19824,14 +19831,14 @@
         <v>0</v>
       </c>
       <c r="AV15" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW15" s="31">
         <v>0</v>
       </c>
       <c r="AX15" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY15" s="31"/>
@@ -19843,7 +19850,7 @@
       <c r="BE15" s="35"/>
       <c r="BF15" s="31"/>
       <c r="BG15" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. МТЗ 3 ст.", note: "Срабатывание на сигнал 3 ступени МТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH15" s="37"/>
@@ -19866,11 +19873,11 @@
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="J16" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="J16" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗОП</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -19947,14 +19954,14 @@
         <v>0</v>
       </c>
       <c r="AV16" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW16" s="31">
         <v>0</v>
       </c>
       <c r="AX16" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY16" s="31"/>
@@ -19966,7 +19973,7 @@
       <c r="BE16" s="35"/>
       <c r="BF16" s="31"/>
       <c r="BG16" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗОП", note: "Срабатывание на сигнал ЗОП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH16" s="37"/>
@@ -19989,11 +19996,11 @@
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="J17" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>11</v>
-      </c>
-      <c r="J17" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗП</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -20070,14 +20077,14 @@
         <v>0</v>
       </c>
       <c r="AV17" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW17" s="31">
         <v>0</v>
       </c>
       <c r="AX17" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY17" s="31"/>
@@ -20089,7 +20096,7 @@
       <c r="BE17" s="35"/>
       <c r="BF17" s="31"/>
       <c r="BG17" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗП", note: "Срабатывание на сигнал ЗП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH17" s="37"/>
@@ -20112,11 +20119,11 @@
       </c>
       <c r="H18" s="25"/>
       <c r="I18" s="25">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="J18" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>14</v>
-      </c>
-      <c r="J18" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ГСОЗЗ</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -20193,14 +20200,14 @@
         <v>0</v>
       </c>
       <c r="AV18" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW18" s="31">
         <v>0</v>
       </c>
       <c r="AX18" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY18" s="31"/>
@@ -20212,7 +20219,7 @@
       <c r="BE18" s="35"/>
       <c r="BF18" s="31"/>
       <c r="BG18" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ГСОЗЗ", note: "Срабатывание на сигнал ГСОЗЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH18" s="37"/>
@@ -20235,11 +20242,11 @@
       </c>
       <c r="H19" s="25"/>
       <c r="I19" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J19" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J19" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЛО ГЗоткл</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -20316,14 +20323,14 @@
         <v>0</v>
       </c>
       <c r="AV19" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW19" s="31">
         <v>0</v>
       </c>
       <c r="AX19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY19" s="31"/>
@@ -20335,7 +20342,7 @@
       <c r="BE19" s="35"/>
       <c r="BF19" s="31"/>
       <c r="BG19" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЛО ГЗоткл", note: "Срабатывание на сигнал ГЗоткл", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH19" s="37"/>
@@ -20358,11 +20365,11 @@
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J20" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J20" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЛО ГЗсигн</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -20439,14 +20446,14 @@
         <v>0</v>
       </c>
       <c r="AV20" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW20" s="31">
         <v>0</v>
       </c>
       <c r="AX20" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY20" s="31"/>
@@ -20458,7 +20465,7 @@
       <c r="BE20" s="35"/>
       <c r="BF20" s="31"/>
       <c r="BG20" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЛО ГЗсигн", note: "Срабатывание на сигнал ГЗсигн", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH20" s="37"/>
@@ -20481,11 +20488,11 @@
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J21" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J21" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЛО ДТм</v>
       </c>
       <c r="K21" s="23" t="s">
@@ -20562,14 +20569,14 @@
         <v>0</v>
       </c>
       <c r="AV21" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW21" s="31">
         <v>0</v>
       </c>
       <c r="AX21" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY21" s="31"/>
@@ -20581,7 +20588,7 @@
       <c r="BE21" s="35"/>
       <c r="BF21" s="31"/>
       <c r="BG21" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЛО ДТм", note: "Срабатывание на сигнал ЛО ДТм", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH21" s="37"/>
@@ -20604,11 +20611,11 @@
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J22" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J22" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЛО ДТо</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -20685,14 +20692,14 @@
         <v>0</v>
       </c>
       <c r="AV22" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW22" s="31">
         <v>0</v>
       </c>
       <c r="AX22" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY22" s="31"/>
@@ -20704,7 +20711,7 @@
       <c r="BE22" s="35"/>
       <c r="BF22" s="31"/>
       <c r="BG22" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЛО ДТо", note: "Срабатывание на сигнал ЛО ДТо", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH22" s="37"/>
@@ -20727,11 +20734,11 @@
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="25">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="J23" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>14</v>
-      </c>
-      <c r="J23" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЛО РД</v>
       </c>
       <c r="K23" s="23" t="s">
@@ -20808,14 +20815,14 @@
         <v>0</v>
       </c>
       <c r="AV23" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW23" s="31">
         <v>0</v>
       </c>
       <c r="AX23" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY23" s="31"/>
@@ -20827,7 +20834,7 @@
       <c r="BE23" s="35"/>
       <c r="BF23" s="31"/>
       <c r="BG23" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЛО РД", note: "Срабатывание на сигнал ЛО РД", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH23" s="37"/>
@@ -20850,11 +20857,11 @@
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J24" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J24" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗСЧ 1ст.</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -20931,14 +20938,14 @@
         <v>0</v>
       </c>
       <c r="AV24" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW24" s="31">
         <v>0</v>
       </c>
       <c r="AX24" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY24" s="31"/>
@@ -20950,7 +20957,7 @@
       <c r="BE24" s="35"/>
       <c r="BF24" s="31"/>
       <c r="BG24" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗСЧ 1ст.", note: "Срабатывание на сигнал 1 ступени ЗСЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH24" s="37"/>
@@ -20973,11 +20980,11 @@
       </c>
       <c r="H25" s="25"/>
       <c r="I25" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J25" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J25" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗСЧ 2ст.</v>
       </c>
       <c r="K25" s="23" t="s">
@@ -21054,14 +21061,14 @@
         <v>0</v>
       </c>
       <c r="AV25" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW25" s="31">
         <v>0</v>
       </c>
       <c r="AX25" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY25" s="31"/>
@@ -21073,7 +21080,7 @@
       <c r="BE25" s="35"/>
       <c r="BF25" s="31"/>
       <c r="BG25" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗСЧ 2ст.", note: "Срабатывание на сигнал 2 ступени ЗСЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH25" s="37"/>
@@ -21096,11 +21103,11 @@
       </c>
       <c r="H26" s="25"/>
       <c r="I26" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J26" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J26" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗПЧ 1ст.</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -21177,14 +21184,14 @@
         <v>0</v>
       </c>
       <c r="AV26" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW26" s="31">
         <v>0</v>
       </c>
       <c r="AX26" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY26" s="31"/>
@@ -21196,7 +21203,7 @@
       <c r="BE26" s="35"/>
       <c r="BF26" s="31"/>
       <c r="BG26" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗПЧ 1ст.", note: "Срабатывание на сигнал 1 ступени ЗПЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH26" s="37"/>
@@ -21219,11 +21226,11 @@
       </c>
       <c r="H27" s="25"/>
       <c r="I27" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J27" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J27" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗПЧ 2ст.</v>
       </c>
       <c r="K27" s="23" t="s">
@@ -21300,14 +21307,14 @@
         <v>0</v>
       </c>
       <c r="AV27" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW27" s="31">
         <v>0</v>
       </c>
       <c r="AX27" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY27" s="31"/>
@@ -21319,7 +21326,7 @@
       <c r="BE27" s="35"/>
       <c r="BF27" s="31"/>
       <c r="BG27" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗПЧ 2ст.", note: "Срабатывание на сигнал 2 ступени ЗПЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH27" s="37"/>
@@ -21342,11 +21349,11 @@
       </c>
       <c r="H28" s="25"/>
       <c r="I28" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J28" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J28" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗИЧ 1ст.</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -21423,14 +21430,14 @@
         <v>0</v>
       </c>
       <c r="AV28" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW28" s="31">
         <v>0</v>
       </c>
       <c r="AX28" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY28" s="31"/>
@@ -21442,7 +21449,7 @@
       <c r="BE28" s="35"/>
       <c r="BF28" s="31"/>
       <c r="BG28" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗИЧ 1ст.", note: "Срабатывание на сигнал 1 ступени ЗИЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH28" s="37"/>
@@ -21465,11 +21472,11 @@
       </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J29" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J29" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗИЧ 2ст.</v>
       </c>
       <c r="K29" s="23" t="s">
@@ -21546,14 +21553,14 @@
         <v>0</v>
       </c>
       <c r="AV29" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW29" s="31">
         <v>0</v>
       </c>
       <c r="AX29" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY29" s="31"/>
@@ -21565,7 +21572,7 @@
       <c r="BE29" s="35"/>
       <c r="BF29" s="31"/>
       <c r="BG29" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗИЧ 2ст.", note: "Срабатывание на сигнал 2 ступени ЗИЧ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH29" s="37"/>
@@ -21588,11 +21595,11 @@
       </c>
       <c r="H30" s="25"/>
       <c r="I30" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J30" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J30" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗМН 1ст.</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -21669,14 +21676,14 @@
         <v>0</v>
       </c>
       <c r="AV30" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW30" s="31">
         <v>0</v>
       </c>
       <c r="AX30" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY30" s="31"/>
@@ -21688,7 +21695,7 @@
       <c r="BE30" s="35"/>
       <c r="BF30" s="31"/>
       <c r="BG30" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗМН 1ст.", note: "Срабатывание на сигнал 1 ступени ЗМН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH30" s="37"/>
@@ -21711,11 +21718,11 @@
       </c>
       <c r="H31" s="25"/>
       <c r="I31" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J31" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J31" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗМН 2ст.</v>
       </c>
       <c r="K31" s="23" t="s">
@@ -21792,14 +21799,14 @@
         <v>0</v>
       </c>
       <c r="AV31" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW31" s="31">
         <v>0</v>
       </c>
       <c r="AX31" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY31" s="31"/>
@@ -21811,7 +21818,7 @@
       <c r="BE31" s="35"/>
       <c r="BF31" s="31"/>
       <c r="BG31" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗМН 2ст.", note: "Срабатывание на сигнал 2 ступени ЗМН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH31" s="37"/>
@@ -21834,11 +21841,11 @@
       </c>
       <c r="H32" s="25"/>
       <c r="I32" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J32" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J32" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Ср.сигн. ЗПН 1ст.</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -21915,14 +21922,14 @@
         <v>0</v>
       </c>
       <c r="AV32" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW32" s="31">
         <v>0</v>
       </c>
       <c r="AX32" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY32" s="31"/>
@@ -21934,7 +21941,7 @@
       <c r="BE32" s="35"/>
       <c r="BF32" s="31"/>
       <c r="BG32" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Ср.сигн. ЗПН 1ст.", note: "Срабатывание на сигнал 1 ступени ЗПН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH32" s="37"/>
@@ -21957,11 +21964,11 @@
       </c>
       <c r="H33" s="25"/>
       <c r="I33" s="25">
-        <f t="shared" ref="I33:I62" si="15">LEN(F33)</f>
+        <f t="shared" ref="I33:I62" si="14">LEN(F33)</f>
         <v>17</v>
       </c>
       <c r="J33" s="25" t="str">
-        <f t="shared" ref="J33:J62" si="16">IF(LEN(F33)&lt;=$J$1,F33,"")</f>
+        <f t="shared" ref="J33:J62" si="15">IF(LEN(F33)&lt;=$J$1,F33,"")</f>
         <v>Ср.сигн. ЗПН 2ст.</v>
       </c>
       <c r="K33" s="23" t="s">
@@ -22038,14 +22045,14 @@
         <v>0</v>
       </c>
       <c r="AV33" s="31">
-        <f t="shared" ref="AV33:AV62" si="17">BIN2DEC(CONCATENATE(0,0,0,0,AR33,AS33,AT33,AU33))</f>
+        <f t="shared" ref="AV33:AV62" si="16">BIN2DEC(CONCATENATE(0,0,0,0,AR33,AS33,AT33,AU33))</f>
         <v>0</v>
       </c>
       <c r="AW33" s="31">
         <v>0</v>
       </c>
       <c r="AX33" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY33" s="31"/>
@@ -22057,7 +22064,7 @@
       <c r="BE33" s="35"/>
       <c r="BF33" s="31"/>
       <c r="BG33" s="36" t="str">
-        <f t="shared" ref="BG33:BG62" si="18">CONCATENATE("description: """,F33,"""", ", ", "note: """,E33,"""",", ","group: """, B33, """",", ","minValue: ", S33,", ","maxValue: ", T33,", ","step: ", U33,", ","units: """, R33, """",", ","defaultValue: ", X33,", ","eventRegistration: ", Y33,)</f>
+        <f t="shared" ref="BG33:BG62" si="17">CONCATENATE("description: """,F33,"""", ", ", "note: """,E33,"""",", ","group: """, B33, """",", ","minValue: ", S33,", ","maxValue: ", T33,", ","step: ", U33,", ","units: """, R33, """",", ","defaultValue: ", X33,", ","eventRegistration: ", Y33,)</f>
         <v>description: "Ср.сигн. ЗПН 2ст.", note: "Срабатывание на сигнал 2 ступени ЗПН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH33" s="37"/>
@@ -22080,11 +22087,11 @@
       </c>
       <c r="H34" s="25"/>
       <c r="I34" s="25">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="J34" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>12</v>
-      </c>
-      <c r="J34" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Ср.сигн. ЗДЗ</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -22161,14 +22168,14 @@
         <v>0</v>
       </c>
       <c r="AV34" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW34" s="31">
         <v>0</v>
       </c>
       <c r="AX34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY34" s="31"/>
@@ -22180,7 +22187,7 @@
       <c r="BE34" s="35"/>
       <c r="BF34" s="31"/>
       <c r="BG34" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Ср.сигн. ЗДЗ", note: "Срабатывание на сигнал ЗДЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH34" s="37"/>
@@ -22203,11 +22210,11 @@
       </c>
       <c r="H35" s="25"/>
       <c r="I35" s="25">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="J35" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>11</v>
-      </c>
-      <c r="J35" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Неиспр. ЗДЗ</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -22284,14 +22291,14 @@
         <v>0</v>
       </c>
       <c r="AV35" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW35" s="31">
         <v>0</v>
       </c>
       <c r="AX35" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY35" s="31"/>
@@ -22303,7 +22310,7 @@
       <c r="BE35" s="35"/>
       <c r="BF35" s="31"/>
       <c r="BG35" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Неиспр. ЗДЗ", note: "Неисправность ЗДЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH35" s="37"/>
@@ -22326,11 +22333,11 @@
       </c>
       <c r="H36" s="25"/>
       <c r="I36" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J36" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J36" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Задержка включ. АПВ</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -22407,14 +22414,14 @@
         <v>0</v>
       </c>
       <c r="AV36" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW36" s="31">
         <v>0</v>
       </c>
       <c r="AX36" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY36" s="31"/>
@@ -22426,7 +22433,7 @@
       <c r="BE36" s="35"/>
       <c r="BF36" s="31"/>
       <c r="BG36" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Задержка включ. АПВ", note: "Задержка включения от АПВ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH36" s="37"/>
@@ -22449,11 +22456,11 @@
       </c>
       <c r="H37" s="25"/>
       <c r="I37" s="25">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="J37" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>15</v>
-      </c>
-      <c r="J37" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Неиспр. ЦН БННш</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -22530,14 +22537,14 @@
         <v>0</v>
       </c>
       <c r="AV37" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW37" s="31">
         <v>0</v>
       </c>
       <c r="AX37" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY37" s="31"/>
@@ -22549,7 +22556,7 @@
       <c r="BE37" s="35"/>
       <c r="BF37" s="31"/>
       <c r="BG37" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Неиспр. ЦН БННш", note: "Неисправность цепей напряжения БНН секции шин", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH37" s="37"/>
@@ -22572,11 +22579,11 @@
       </c>
       <c r="H38" s="25"/>
       <c r="I38" s="25">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="J38" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>15</v>
-      </c>
-      <c r="J38" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Неиспр. ЦН БННп</v>
       </c>
       <c r="K38" s="23" t="s">
@@ -22653,14 +22660,14 @@
         <v>0</v>
       </c>
       <c r="AV38" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW38" s="31">
         <v>0</v>
       </c>
       <c r="AX38" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY38" s="31"/>
@@ -22672,7 +22679,7 @@
       <c r="BE38" s="35"/>
       <c r="BF38" s="31"/>
       <c r="BG38" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Неиспр. ЦН БННп", note: "Неисправность цепей напряжения БНН присоединения", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH38" s="37"/>
@@ -22695,11 +22702,11 @@
       </c>
       <c r="H39" s="25"/>
       <c r="I39" s="25">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="J39" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>15</v>
-      </c>
-      <c r="J39" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Неисправность В</v>
       </c>
       <c r="K39" s="23" t="s">
@@ -22776,14 +22783,14 @@
         <v>0</v>
       </c>
       <c r="AV39" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW39" s="31">
         <v>0</v>
       </c>
       <c r="AX39" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY39" s="31"/>
@@ -22795,7 +22802,7 @@
       <c r="BE39" s="35"/>
       <c r="BF39" s="31"/>
       <c r="BG39" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Неисправность В", note: "Неисправность выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH39" s="37"/>
@@ -22818,11 +22825,11 @@
       </c>
       <c r="H40" s="25"/>
       <c r="I40" s="25">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="J40" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>17</v>
-      </c>
-      <c r="J40" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Превышен ресурс В</v>
       </c>
       <c r="K40" s="23" t="s">
@@ -22899,14 +22906,14 @@
         <v>0</v>
       </c>
       <c r="AV40" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW40" s="31">
         <v>0</v>
       </c>
       <c r="AX40" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY40" s="31"/>
@@ -22918,7 +22925,7 @@
       <c r="BE40" s="35"/>
       <c r="BF40" s="31"/>
       <c r="BG40" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Превышен ресурс В", note: "Превышен ресурс выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH40" s="37"/>
@@ -23064,11 +23071,11 @@
       </c>
       <c r="H42" s="25"/>
       <c r="I42" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J42" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J42" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Отключение от ЛО РЗ</v>
       </c>
       <c r="K42" s="23" t="s">
@@ -23145,14 +23152,14 @@
         <v>0</v>
       </c>
       <c r="AV42" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW42" s="31">
         <v>0</v>
       </c>
       <c r="AX42" s="31">
-        <f t="shared" ref="AX42:AX62" si="19">BIN2DEC(CONCATENATE(0,0,0,0,AT42,AU42,AV42,AW42))</f>
+        <f t="shared" ref="AX42:AX62" si="18">BIN2DEC(CONCATENATE(0,0,0,0,AT42,AU42,AV42,AW42))</f>
         <v>0</v>
       </c>
       <c r="AY42" s="31"/>
@@ -23164,7 +23171,7 @@
       <c r="BE42" s="35"/>
       <c r="BF42" s="31"/>
       <c r="BG42" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Отключение от ЛО РЗ", note: "Отключение от ЛО РЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH42" s="37"/>
@@ -23187,11 +23194,11 @@
       </c>
       <c r="H43" s="25"/>
       <c r="I43" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J43" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J43" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Отключить от ЛО ПА</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -23268,14 +23275,14 @@
         <v>0</v>
       </c>
       <c r="AV43" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW43" s="31">
         <v>0</v>
       </c>
       <c r="AX43" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY43" s="31"/>
@@ -23287,7 +23294,7 @@
       <c r="BE43" s="35"/>
       <c r="BF43" s="31"/>
       <c r="BG43" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Отключить от ЛО ПА", note: "Отключить от ЛО ПА", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH43" s="37"/>
@@ -23310,11 +23317,11 @@
       </c>
       <c r="H44" s="25"/>
       <c r="I44" s="25">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="J44" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>17</v>
-      </c>
-      <c r="J44" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Срабатывание УРОВ</v>
       </c>
       <c r="K44" s="23" t="s">
@@ -23391,14 +23398,14 @@
         <v>0</v>
       </c>
       <c r="AV44" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW44" s="31">
         <v>0</v>
       </c>
       <c r="AX44" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY44" s="31"/>
@@ -23410,7 +23417,7 @@
       <c r="BE44" s="35"/>
       <c r="BF44" s="31"/>
       <c r="BG44" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Срабатывание УРОВ", note: "Срабатывание УРОВ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH44" s="37"/>
@@ -23422,22 +23429,22 @@
       </c>
       <c r="C45" s="24"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="63" t="s">
+      <c r="E45" s="61" t="s">
         <v>316</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="60" t="s">
         <v>317</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="60" t="s">
         <v>317</v>
       </c>
       <c r="H45" s="25"/>
       <c r="I45" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J45" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J45" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Сраб. УРОВ на себя</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -23514,14 +23521,14 @@
         <v>0</v>
       </c>
       <c r="AV45" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW45" s="31">
         <v>0</v>
       </c>
       <c r="AX45" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY45" s="31"/>
@@ -23533,7 +23540,7 @@
       <c r="BE45" s="35"/>
       <c r="BF45" s="31"/>
       <c r="BG45" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Сраб. УРОВ на себя", note: "Срабатывание УРОВ &lt;&lt;на себя&gt;&gt;", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH45" s="37"/>
@@ -23556,11 +23563,11 @@
       </c>
       <c r="H46" s="25"/>
       <c r="I46" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J46" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J46" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>В самопр. отключен</v>
       </c>
       <c r="K46" s="23" t="s">
@@ -23637,14 +23644,14 @@
         <v>0</v>
       </c>
       <c r="AV46" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW46" s="31">
         <v>0</v>
       </c>
       <c r="AX46" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY46" s="31"/>
@@ -23656,7 +23663,7 @@
       <c r="BE46" s="35"/>
       <c r="BF46" s="31"/>
       <c r="BG46" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "В самопр. отключен", note: "Выключатель самопроизвольно отключен", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH46" s="37"/>
@@ -23679,11 +23686,11 @@
       </c>
       <c r="H47" s="25"/>
       <c r="I47" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J47" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J47" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Зад. вкл с КС от КП</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -23760,14 +23767,14 @@
         <v>0</v>
       </c>
       <c r="AV47" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW47" s="31">
         <v>0</v>
       </c>
       <c r="AX47" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY47" s="31"/>
@@ -23779,7 +23786,7 @@
       <c r="BE47" s="35"/>
       <c r="BF47" s="31"/>
       <c r="BG47" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Зад. вкл с КС от КП", note: "Задержка включения с контролем синхронизма от КП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH47" s="37"/>
@@ -23802,11 +23809,11 @@
       </c>
       <c r="H48" s="25"/>
       <c r="I48" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J48" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J48" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Зад. вкл с КС от УВ</v>
       </c>
       <c r="K48" s="23" t="s">
@@ -23883,14 +23890,14 @@
         <v>0</v>
       </c>
       <c r="AV48" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW48" s="31">
         <v>0</v>
       </c>
       <c r="AX48" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY48" s="31"/>
@@ -23902,7 +23909,7 @@
       <c r="BE48" s="35"/>
       <c r="BF48" s="31"/>
       <c r="BG48" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Зад. вкл с КС от УВ", note: "Задержка включения с контролем синхронизма от УВ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH48" s="37"/>
@@ -23925,11 +23932,11 @@
       </c>
       <c r="H49" s="25"/>
       <c r="I49" s="25">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="J49" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>13</v>
-      </c>
-      <c r="J49" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>ТЗ сигн от СС</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -24006,14 +24013,14 @@
         <v>0</v>
       </c>
       <c r="AV49" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW49" s="31">
         <v>0</v>
       </c>
       <c r="AX49" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY49" s="31"/>
@@ -24025,7 +24032,7 @@
       <c r="BE49" s="35"/>
       <c r="BF49" s="31"/>
       <c r="BG49" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "ТЗ сигн от СС", note: "Сигнализация ТЗ (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH49" s="37"/>
@@ -24048,11 +24055,11 @@
       </c>
       <c r="H50" s="25"/>
       <c r="I50" s="25">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="J50" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>13</v>
-      </c>
-      <c r="J50" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>ГЗ сигн от СС</v>
       </c>
       <c r="K50" s="23" t="s">
@@ -24129,14 +24136,14 @@
         <v>0</v>
       </c>
       <c r="AV50" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW50" s="31">
         <v>0</v>
       </c>
       <c r="AX50" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY50" s="31"/>
@@ -24148,7 +24155,7 @@
       <c r="BE50" s="35"/>
       <c r="BF50" s="31"/>
       <c r="BG50" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "ГЗ сигн от СС", note: "Сигнализация ГЗ (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH50" s="37"/>
@@ -24171,11 +24178,11 @@
       </c>
       <c r="H51" s="25"/>
       <c r="I51" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J51" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J51" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Низ.изол. ТЗ от СС</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -24252,14 +24259,14 @@
         <v>0</v>
       </c>
       <c r="AV51" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW51" s="31">
         <v>0</v>
       </c>
       <c r="AX51" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY51" s="31"/>
@@ -24271,7 +24278,7 @@
       <c r="BE51" s="35"/>
       <c r="BF51" s="31"/>
       <c r="BG51" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Низ.изол. ТЗ от СС", note: "Низкая изоляция ТЗ (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH51" s="37"/>
@@ -24294,11 +24301,11 @@
       </c>
       <c r="H52" s="25"/>
       <c r="I52" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J52" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J52" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Низ.изол. ГЗ от СС</v>
       </c>
       <c r="K52" s="23" t="s">
@@ -24375,14 +24382,14 @@
         <v>0</v>
       </c>
       <c r="AV52" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW52" s="31">
         <v>0</v>
       </c>
       <c r="AX52" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY52" s="31"/>
@@ -24394,7 +24401,7 @@
       <c r="BE52" s="35"/>
       <c r="BF52" s="31"/>
       <c r="BG52" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Низ.изол. ГЗ от СС", note: "Низкая изоляция ГЗ (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH52" s="37"/>
@@ -24417,11 +24424,11 @@
       </c>
       <c r="H53" s="25"/>
       <c r="I53" s="25">
+        <f t="shared" si="14"/>
+        <v>16</v>
+      </c>
+      <c r="J53" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>16</v>
-      </c>
-      <c r="J53" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>ТЗ заблок. от СС</v>
       </c>
       <c r="K53" s="23" t="s">
@@ -24498,14 +24505,14 @@
         <v>0</v>
       </c>
       <c r="AV53" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW53" s="31">
         <v>0</v>
       </c>
       <c r="AX53" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY53" s="31"/>
@@ -24517,7 +24524,7 @@
       <c r="BE53" s="35"/>
       <c r="BF53" s="31"/>
       <c r="BG53" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "ТЗ заблок. от СС", note: "ТЗ заблокирована (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH53" s="37"/>
@@ -24540,11 +24547,11 @@
       </c>
       <c r="H54" s="25"/>
       <c r="I54" s="25">
-        <f t="shared" ref="I54" si="20">LEN(F54)</f>
+        <f t="shared" ref="I54" si="19">LEN(F54)</f>
         <v>16</v>
       </c>
       <c r="J54" s="25" t="str">
-        <f t="shared" ref="J54" si="21">IF(LEN(F54)&lt;=$J$1,F54,"")</f>
+        <f t="shared" ref="J54" si="20">IF(LEN(F54)&lt;=$J$1,F54,"")</f>
         <v>ГЗ заблок. от СС</v>
       </c>
       <c r="K54" s="23" t="s">
@@ -24621,14 +24628,14 @@
         <v>0</v>
       </c>
       <c r="AV54" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW54" s="31">
         <v>0</v>
       </c>
       <c r="AX54" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY54" s="31"/>
@@ -24640,7 +24647,7 @@
       <c r="BE54" s="35"/>
       <c r="BF54" s="31"/>
       <c r="BG54" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "ГЗ заблок. от СС", note: "ГЗ заблокирована (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH54" s="37"/>
@@ -24663,11 +24670,11 @@
       </c>
       <c r="H55" s="25"/>
       <c r="I55" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J55" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J55" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Цепи разобр. от СС</v>
       </c>
       <c r="K55" s="23" t="s">
@@ -24744,14 +24751,14 @@
         <v>0</v>
       </c>
       <c r="AV55" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW55" s="31">
         <v>0</v>
       </c>
       <c r="AX55" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY55" s="31"/>
@@ -24763,7 +24770,7 @@
       <c r="BE55" s="35"/>
       <c r="BF55" s="31"/>
       <c r="BG55" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Цепи разобр. от СС", note: "Выходные цепи разобраны (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH55" s="37"/>
@@ -24786,11 +24793,11 @@
       </c>
       <c r="H56" s="25"/>
       <c r="I56" s="25">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="J56" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>17</v>
-      </c>
-      <c r="J56" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>БИ выведены от СС</v>
       </c>
       <c r="K56" s="23" t="s">
@@ -24867,14 +24874,14 @@
         <v>0</v>
       </c>
       <c r="AV56" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW56" s="31">
         <v>0</v>
       </c>
       <c r="AX56" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY56" s="31"/>
@@ -24886,7 +24893,7 @@
       <c r="BE56" s="35"/>
       <c r="BF56" s="31"/>
       <c r="BG56" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "БИ выведены от СС", note: "БИ выведены (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH56" s="37"/>
@@ -24909,11 +24916,11 @@
       </c>
       <c r="H57" s="25"/>
       <c r="I57" s="25">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="J57" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>13</v>
-      </c>
-      <c r="J57" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>ОТ сигн от СС</v>
       </c>
       <c r="K57" s="23" t="s">
@@ -24990,14 +24997,14 @@
         <v>0</v>
       </c>
       <c r="AV57" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW57" s="31">
         <v>0</v>
       </c>
       <c r="AX57" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY57" s="31"/>
@@ -25009,7 +25016,7 @@
       <c r="BE57" s="35"/>
       <c r="BF57" s="31"/>
       <c r="BG57" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "ОТ сигн от СС", note: "Сигнализация опер.тока (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH57" s="37"/>
@@ -25032,11 +25039,11 @@
       </c>
       <c r="H58" s="25"/>
       <c r="I58" s="25">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="J58" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>15</v>
-      </c>
-      <c r="J58" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Неиспр КА от СС</v>
       </c>
       <c r="K58" s="23" t="s">
@@ -25113,14 +25120,14 @@
         <v>0</v>
       </c>
       <c r="AV58" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW58" s="31">
         <v>0</v>
       </c>
       <c r="AX58" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY58" s="31"/>
@@ -25132,7 +25139,7 @@
       <c r="BE58" s="35"/>
       <c r="BF58" s="31"/>
       <c r="BG58" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Неиспр КА от СС", note: "Неисправность КА (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH58" s="37"/>
@@ -25155,11 +25162,11 @@
       </c>
       <c r="H59" s="25"/>
       <c r="I59" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J59" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J59" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Прев.вр.пер. от СС</v>
       </c>
       <c r="K59" s="23" t="s">
@@ -25236,14 +25243,14 @@
         <v>0</v>
       </c>
       <c r="AV59" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW59" s="31">
         <v>0</v>
       </c>
       <c r="AX59" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY59" s="31"/>
@@ -25255,7 +25262,7 @@
       <c r="BE59" s="35"/>
       <c r="BF59" s="31"/>
       <c r="BG59" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Прев.вр.пер. от СС", note: "Превышение времени переключения КА (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH59" s="37"/>
@@ -25278,11 +25285,11 @@
       </c>
       <c r="H60" s="25"/>
       <c r="I60" s="25">
-        <f t="shared" ref="I60" si="22">LEN(F60)</f>
+        <f t="shared" ref="I60" si="21">LEN(F60)</f>
         <v>18</v>
       </c>
       <c r="J60" s="25" t="str">
-        <f t="shared" ref="J60" si="23">IF(LEN(F60)&lt;=$J$1,F60,"")</f>
+        <f t="shared" ref="J60" si="22">IF(LEN(F60)&lt;=$J$1,F60,"")</f>
         <v>Общ.вн.сигн. от СС</v>
       </c>
       <c r="K60" s="23" t="s">
@@ -25359,14 +25366,14 @@
         <v>0</v>
       </c>
       <c r="AV60" s="31">
-        <f t="shared" ref="AV60" si="24">BIN2DEC(CONCATENATE(0,0,0,0,AR60,AS60,AT60,AU60))</f>
+        <f t="shared" ref="AV60" si="23">BIN2DEC(CONCATENATE(0,0,0,0,AR60,AS60,AT60,AU60))</f>
         <v>0</v>
       </c>
       <c r="AW60" s="31">
         <v>0</v>
       </c>
       <c r="AX60" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY60" s="31"/>
@@ -25378,7 +25385,7 @@
       <c r="BE60" s="35"/>
       <c r="BF60" s="31"/>
       <c r="BG60" s="36" t="str">
-        <f t="shared" ref="BG60" si="25">CONCATENATE("description: """,F60,"""", ", ", "note: """,E60,"""",", ","group: """, B60, """",", ","minValue: ", S60,", ","maxValue: ", T60,", ","step: ", U60,", ","units: """, R60, """",", ","defaultValue: ", X60,", ","eventRegistration: ", Y60,)</f>
+        <f t="shared" ref="BG60" si="24">CONCATENATE("description: """,F60,"""", ", ", "note: """,E60,"""",", ","group: """, B60, """",", ","minValue: ", S60,", ","maxValue: ", T60,", ","step: ", U60,", ","units: """, R60, """",", ","defaultValue: ", X60,", ","eventRegistration: ", Y60,)</f>
         <v>description: "Общ.вн.сигн. от СС", note: "Общий внешний сигнал (от функции сборка сигналов)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH60" s="37"/>
@@ -25401,11 +25408,11 @@
       </c>
       <c r="H61" s="25"/>
       <c r="I61" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J61" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J61" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Полож.пер.ав.дебл.</v>
       </c>
       <c r="K61" s="23" t="s">
@@ -25482,14 +25489,14 @@
         <v>0</v>
       </c>
       <c r="AV61" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW61" s="31">
         <v>0</v>
       </c>
       <c r="AX61" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY61" s="31"/>
@@ -25501,7 +25508,7 @@
       <c r="BE61" s="35"/>
       <c r="BF61" s="31"/>
       <c r="BG61" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Полож.пер.ав.дебл.", note: "Положение переключателя аварийной деблокировки", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH61" s="37"/>
@@ -25524,11 +25531,11 @@
       </c>
       <c r="H62" s="25"/>
       <c r="I62" s="25">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="J62" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="J62" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>IRF</v>
       </c>
       <c r="K62" s="23" t="s">
@@ -25605,14 +25612,14 @@
         <v>0</v>
       </c>
       <c r="AV62" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW62" s="31">
         <v>0</v>
       </c>
       <c r="AX62" s="31">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AY62" s="31"/>
@@ -25624,7 +25631,7 @@
       <c r="BE62" s="35"/>
       <c r="BF62" s="31"/>
       <c r="BG62" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "IRF", note: "Внутренняя неисправность", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH62" s="37"/>
@@ -29465,15 +29472,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="54"/>
-      <c r="BB1" s="54"/>
-      <c r="BC1" s="54"/>
-      <c r="BD1" s="54"/>
-      <c r="BE1" s="54"/>
-      <c r="BF1" s="54"/>
+      <c r="AZ1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -29617,13 +29624,13 @@
       <c r="AU2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="AV2" s="60" t="s">
+      <c r="AV2" s="58" t="s">
         <v>312</v>
       </c>
-      <c r="AW2" s="60" t="s">
+      <c r="AW2" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="AX2" s="60" t="s">
+      <c r="AX2" s="58" t="s">
         <v>314</v>
       </c>
       <c r="AY2" s="19"/>
@@ -45974,7 +45981,7 @@
     </row>
     <row r="3" spans="1:16379" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="57" t="s">
         <v>311</v>
       </c>
       <c r="C3" s="39"/>
@@ -46096,7 +46103,7 @@
     </row>
     <row r="4" spans="1:16379" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="57" t="s">
         <v>311</v>
       </c>
       <c r="C4" s="39"/>
@@ -46323,15 +46330,15 @@
       <c r="AX1" s="11"/>
       <c r="AY1" s="11"/>
       <c r="AZ1" s="13"/>
-      <c r="BA1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB1" s="54"/>
-      <c r="BC1" s="54"/>
-      <c r="BD1" s="54"/>
-      <c r="BE1" s="54"/>
-      <c r="BF1" s="54"/>
-      <c r="BG1" s="54"/>
+      <c r="BA1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
     </row>
     <row r="2" spans="1:16380" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -46355,7 +46362,7 @@
       <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="55" t="s">
         <v>310</v>
       </c>
       <c r="I2" s="14" t="s">
@@ -62851,7 +62858,7 @@
       <c r="G3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" s="56" t="s">
         <v>75</v>
       </c>
       <c r="I3" s="26" t="s">
@@ -62979,7 +62986,7 @@
       <c r="G4" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="56" t="s">
         <v>76</v>
       </c>
       <c r="I4" s="26" t="s">
@@ -63107,7 +63114,7 @@
       <c r="G5" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="56" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="26" t="s">
@@ -63235,7 +63242,7 @@
       <c r="G6" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="56" t="s">
         <v>78</v>
       </c>
       <c r="I6" s="26" t="s">
@@ -63363,7 +63370,7 @@
       <c r="G7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="56" t="s">
         <v>80</v>
       </c>
       <c r="I7" s="26" t="s">
@@ -63491,7 +63498,7 @@
       <c r="G8" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="56" t="s">
         <v>250</v>
       </c>
       <c r="I8" s="26" t="s">
@@ -63619,7 +63626,7 @@
       <c r="G9" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="56" t="s">
         <v>251</v>
       </c>
       <c r="I9" s="26" t="s">
@@ -63747,7 +63754,7 @@
       <c r="G10" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" s="56" t="s">
         <v>252</v>
       </c>
       <c r="I10" s="26" t="s">
@@ -63875,7 +63882,7 @@
       <c r="G11" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="56" t="s">
         <v>253</v>
       </c>
       <c r="I11" s="26" t="s">
@@ -64003,7 +64010,7 @@
       <c r="G12" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="56" t="s">
         <v>254</v>
       </c>
       <c r="I12" s="26" t="s">
@@ -64131,7 +64138,7 @@
       <c r="G13" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="56" t="s">
         <v>255</v>
       </c>
       <c r="I13" s="26" t="s">
@@ -64259,7 +64266,7 @@
       <c r="G14" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="56" t="s">
         <v>256</v>
       </c>
       <c r="I14" s="26" t="s">
@@ -64387,7 +64394,7 @@
       <c r="G15" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="56" t="s">
         <v>288</v>
       </c>
       <c r="I15" s="26" t="s">
@@ -64565,7 +64572,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="53" t="s">
         <v>307</v>
       </c>
       <c r="B8" t="s">
@@ -64573,13 +64580,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="53" t="s">
         <v>309</v>
       </c>
-      <c r="B9" s="55"/>
+      <c r="B9" s="53"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="54" t="s">
         <v>247</v>
       </c>
       <c r="B10" t="s">
@@ -64587,10 +64594,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="53" t="s">
         <v>309</v>
       </c>
-      <c r="B11" s="55"/>
+      <c r="B11" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
